--- a/data/trans_camb/IP18A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Estudios-trans_camb.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 1,89</t>
+          <t>-5,78; 1,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 0,0</t>
+          <t>-7,43; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 54,36</t>
+          <t>-2,21; 50,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,27</t>
+          <t>-3,07; 1,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,12</t>
+          <t>-2,65; 1,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 32,85</t>
+          <t>-0,67; 35,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,25</t>
+          <t>-0,93; 1,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,57</t>
+          <t>-0,7; 1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,0</t>
+          <t>-0,75; 5,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,1</t>
+          <t>-0,5; 1,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,06</t>
+          <t>0,39; 2,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,98</t>
+          <t>0,96; 9,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,88</t>
+          <t>-0,42; 0,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,85</t>
+          <t>0,26; 2,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,78</t>
+          <t>1,01; 6,67</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,29; 438,91</t>
+          <t>-77,88; 487,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 856,9</t>
+          <t>-66,88; 600,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3623,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,93; —</t>
+          <t>-15,34; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,54; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 342,37</t>
+          <t>-53,57; 380,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 651,66</t>
+          <t>8,72; 729,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,87; 2046,26</t>
+          <t>86,73; 2431,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,16</t>
+          <t>-1,54; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,57</t>
+          <t>-1,2; 1,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 15,0</t>
+          <t>0,81; 16,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,16</t>
+          <t>0,64; 5,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,21</t>
+          <t>-0,61; 2,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,68</t>
+          <t>0,08; 2,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,45</t>
+          <t>-0,63; 1,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,46</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,7; —</t>
+          <t>-44,03; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,02</t>
+          <t>-0,64; 1,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,48</t>
+          <t>-0,3; 1,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,35</t>
+          <t>0,21; 5,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,45</t>
+          <t>-0,27; 1,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,87</t>
+          <t>0,03; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,15</t>
+          <t>1,1; 8,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,03</t>
+          <t>-0,15; 0,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,4</t>
+          <t>0,09; 1,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,86</t>
+          <t>1,35; 5,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 378,1</t>
+          <t>-64,24; 345,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 642,13</t>
+          <t>-48,2; 507,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 2083,33</t>
+          <t>-22,09; 1973,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 659,84</t>
+          <t>-37,99; 721,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 691,57</t>
+          <t>-10,06; 872,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,46; 3032,52</t>
+          <t>77,08; 2949,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 331,66</t>
+          <t>-22,23; 299,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 371,45</t>
+          <t>3,66; 403,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>164,28; 1515,59</t>
+          <t>155,96; 1496,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Estudios-trans_camb.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 1,91</t>
+          <t>-6,0; 1,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,0</t>
+          <t>-7,47; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 50,44</t>
+          <t>-2,23; 47,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,32</t>
+          <t>-2,96; 1,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,74</t>
+          <t>-2,27; 2,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 35,11</t>
+          <t>-0,98; 34,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,26</t>
+          <t>-0,92; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,59</t>
+          <t>-0,73; 1,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,98</t>
+          <t>-0,74; 5,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,1</t>
+          <t>-0,42; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,81</t>
+          <t>0,43; 3,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,86</t>
+          <t>1,1; 10,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,93</t>
+          <t>-0,45; 0,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,04</t>
+          <t>0,11; 1,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,67</t>
+          <t>0,62; 6,52</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 487,93</t>
+          <t>-72,64; 534,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,88; 600,88</t>
+          <t>-67,21; 696,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,34; —</t>
+          <t>-14,51; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,54; —</t>
+          <t>-14,75; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 380,43</t>
+          <t>-54,06; 344,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 729,59</t>
+          <t>-2,55; 698,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,73; 2431,21</t>
+          <t>55,33; 2264,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,02</t>
+          <t>-1,55; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,6</t>
+          <t>-1,18; 1,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 16,57</t>
+          <t>0,38; 14,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,52</t>
+          <t>0,58; 4,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,38</t>
+          <t>-0,6; 2,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,0</t>
+          <t>-1,75; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,64</t>
+          <t>-0,06; 2,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,48</t>
+          <t>-0,49; 1,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,02; 6,97</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,03; —</t>
+          <t>-55,95; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,02</t>
+          <t>-0,64; 1,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,43</t>
+          <t>-0,26; 1,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,72</t>
+          <t>0,31; 5,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,44</t>
+          <t>-0,25; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,87</t>
+          <t>-0,06; 1,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,58</t>
+          <t>1,2; 8,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,99</t>
+          <t>-0,12; 0,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,39</t>
+          <t>0,09; 1,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,95</t>
+          <t>1,27; 5,74</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 345,79</t>
+          <t>-70,37; 416,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 507,61</t>
+          <t>-39,25; 664,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 1973,84</t>
+          <t>-27,18; 1789,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 721,28</t>
+          <t>-48,94; 507,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 872,21</t>
+          <t>-25,72; 677,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,08; 2949,13</t>
+          <t>92,17; 3276,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 299,21</t>
+          <t>-18,97; 335,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 403,36</t>
+          <t>-1,13; 442,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>155,96; 1496,99</t>
+          <t>152,75; 1646,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,76</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,12</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-0,29</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>11,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>-5,72; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>-6,94; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,24; 52,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 1,83</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,0</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 47,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,3</t>
+          <t>-2,74; 1,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,16</t>
+          <t>-2,45; 2,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 34,42</t>
+          <t>-1,07; 33,35</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-57,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>837,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-57,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>807,55%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-25,38%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>947,23%</t>
+          <t>1007,03%</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,3</t>
+          <t>-0,52; 1,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,55</t>
+          <t>0,46; 3,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,74</t>
+          <t>1,11; 12,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,09</t>
+          <t>-0,99; 1,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,0</t>
+          <t>-0,69; 1,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,14</t>
+          <t>-0,66; 7,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,93</t>
+          <t>-0,45; 0,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,82</t>
+          <t>0,13; 1,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,52</t>
+          <t>0,71; 7,36</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>85,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>447,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1174,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>26,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>48,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>156,47%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85,9%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>447,92%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1133,79%</t>
+          <t>170,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>492,66%</t>
+          <t>512,0%</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,64; 534,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,21; 696,33</t>
+          <t>-11,93; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,29; 438,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,51; —</t>
+          <t>-62,86; 856,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,75; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 344,41</t>
+          <t>-59,42; 342,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 698,73</t>
+          <t>-9,39; 651,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,33; 2264,08</t>
+          <t>57,74; 2180,65</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,02</t>
+          <t>0,63; 5,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,6</t>
+          <t>-0,35; 2,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 14,82</t>
+          <t>-1,74; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,99</t>
+          <t>-1,56; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,53</t>
+          <t>-1,23; 1,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,0</t>
+          <t>0,38; 14,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,56</t>
+          <t>0,04; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,5</t>
+          <t>-0,73; 1,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 6,97</t>
+          <t>0,06; 7,19</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>648,82%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>148,27%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,45%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>51,62%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1008,32%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>648,82%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>148,27%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>938,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>518,57%</t>
+          <t>487,23%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,95; —</t>
+          <t>-53,7; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>3,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,03</t>
+          <t>-0,18; 1,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,51</t>
+          <t>0,02; 1,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,92</t>
+          <t>1,44; 9,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,34</t>
+          <t>-0,65; 1,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,79</t>
+          <t>-0,25; 1,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,58</t>
+          <t>0,29; 6,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,98</t>
+          <t>-0,15; 1,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,41</t>
+          <t>0,07; 1,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,74</t>
+          <t>1,43; 6,17</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>151,49%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700,93%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>36,36%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>86,94%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>365,61%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>151,49%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>668,14%</t>
+          <t>363,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>527,11%</t>
+          <t>541,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 416,36</t>
+          <t>-35,13; 659,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 664,98</t>
+          <t>-15,79; 691,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 1789,85</t>
+          <t>72,54; 3262,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,94; 507,89</t>
+          <t>-64,21; 378,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 677,49</t>
+          <t>-45,36; 642,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,17; 3276,06</t>
+          <t>-25,93; 2111,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 335,58</t>
+          <t>-25,72; 331,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 442,6</t>
+          <t>-6,33; 371,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>152,75; 1646,36</t>
+          <t>167,43; 1577,24</t>
         </is>
       </c>
     </row>
